--- a/diseases/d201/2026-2029.xlsx
+++ b/diseases/d201/2026-2029.xlsx
@@ -1427,6 +1427,441 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>D201</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>exanthematous-diseases</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Exanthematous diseases</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>D201</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Exanthematous diseases</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>出疹性疾病</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>439</v>
+      </c>
+      <c r="O7" t="n">
+        <v>439</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.2055602728672617</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>D201</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>exanthematous-diseases</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Exanthematous diseases</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>D201</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Exanthematous diseases</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>出疹性疾病</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>2044</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2044</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.9570961224161341</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D201</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>exanthematous-diseases</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Exanthematous diseases</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>D201</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Exanthematous diseases</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>出疹性疾病</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>289</v>
+      </c>
+      <c r="O9" t="n">
+        <v>289</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.1353232775823203</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1460,7 +1895,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1978,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -1553,7 +1988,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -1605,7 +2040,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>873</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d201/2026-2029.xlsx
+++ b/diseases/d201/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1057,6 +1067,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1193,6 +1208,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1329,6 +1349,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1465,6 +1490,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1601,6 +1631,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1737,6 +1772,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1873,6 +1913,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2009,6 +2054,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2145,6 +2195,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2281,6 +2336,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2417,6 +2477,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2553,6 +2618,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2689,6 +2759,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2825,6 +2900,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2961,6 +3041,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3097,6 +3182,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3233,6 +3323,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3369,6 +3464,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3505,6 +3605,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3641,6 +3746,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3777,6 +3887,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3913,6 +4028,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4049,6 +4169,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4185,6 +4310,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4321,6 +4451,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4457,6 +4592,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4596,6 +4736,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4741,6 +4886,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4877,6 +5027,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5013,6 +5168,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5149,6 +5309,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5285,6 +5450,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5421,6 +5591,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5557,6 +5732,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5693,6 +5873,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5829,6 +6014,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5965,6 +6155,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6101,6 +6296,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6237,6 +6437,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6373,6 +6578,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6509,6 +6719,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6645,6 +6860,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6781,6 +7001,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6917,6 +7142,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7053,6 +7283,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7189,6 +7424,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7325,6 +7565,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7461,6 +7706,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7597,6 +7847,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7733,6 +7988,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7869,6 +8129,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8005,6 +8270,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8141,6 +8411,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8277,6 +8552,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8416,6 +8696,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8561,6 +8846,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8697,6 +8987,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8833,6 +9128,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8969,6 +9269,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9105,6 +9410,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9241,6 +9551,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9377,6 +9692,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9513,6 +9833,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9649,6 +9974,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9785,6 +10115,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9921,6 +10256,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10057,6 +10397,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10193,6 +10538,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10329,6 +10679,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10465,6 +10820,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10601,6 +10961,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10737,6 +11102,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10873,6 +11243,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11009,6 +11384,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11145,6 +11525,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11281,6 +11666,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11417,6 +11807,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11553,6 +11948,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11689,6 +12089,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11825,6 +12230,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11961,6 +12371,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12097,6 +12512,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12233,6 +12653,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12378,6 +12803,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12514,6 +12944,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12650,6 +13085,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12786,6 +13226,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12922,6 +13367,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13058,6 +13508,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13194,6 +13649,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13330,6 +13790,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13466,6 +13931,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13602,6 +14072,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13738,6 +14213,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13874,6 +14354,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14010,6 +14495,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14146,6 +14636,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14282,6 +14777,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14418,6 +14918,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14554,6 +15059,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14690,6 +15200,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14826,6 +15341,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14962,6 +15482,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15098,6 +15623,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15234,6 +15764,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15370,6 +15905,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15506,6 +16046,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15642,6 +16187,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15778,6 +16328,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15914,6 +16469,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16050,6 +16610,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16195,6 +16760,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16331,6 +16901,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16467,6 +17042,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16603,6 +17183,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16739,6 +17324,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16875,6 +17465,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17011,6 +17606,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17147,6 +17747,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17283,6 +17888,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17419,6 +18029,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17555,6 +18170,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17691,6 +18311,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17827,6 +18452,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17963,6 +18593,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18099,6 +18734,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18235,6 +18875,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18371,6 +19016,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18507,6 +19157,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18643,6 +19298,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18779,6 +19439,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18915,6 +19580,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19051,6 +19721,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19187,6 +19862,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19323,6 +20003,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19459,6 +20144,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19595,6 +20285,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19731,6 +20426,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19867,6 +20567,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20003,6 +20708,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20139,6 +20849,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20275,6 +20990,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20411,6 +21131,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20547,6 +21272,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20683,6 +21413,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20819,6 +21554,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20955,6 +21695,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21091,6 +21836,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21227,6 +21977,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21363,6 +22118,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21499,6 +22259,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21635,6 +22400,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21771,6 +22541,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21907,6 +22682,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22043,6 +22823,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22179,6 +22964,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22315,6 +23105,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22451,6 +23246,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22587,6 +23387,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22723,6 +23528,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22859,6 +23669,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22995,6 +23810,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23131,6 +23951,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23267,6 +24092,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23403,6 +24233,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23539,6 +24374,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23684,6 +24524,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23820,6 +24665,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23956,6 +24806,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24092,6 +24947,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24228,6 +25088,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24364,6 +25229,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24500,6 +25370,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24636,6 +25511,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24772,6 +25652,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24908,6 +25793,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25044,6 +25934,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25180,6 +26075,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25316,6 +26216,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25452,6 +26357,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25588,6 +26498,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25724,6 +26639,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25860,6 +26780,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25996,6 +26921,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26132,6 +27062,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26268,6 +27203,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26404,6 +27344,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26540,6 +27485,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26676,6 +27626,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26812,6 +27767,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26948,6 +27908,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27084,6 +28049,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27220,6 +28190,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27356,6 +28331,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27501,6 +28481,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27637,6 +28622,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27773,6 +28763,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27909,6 +28904,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28045,6 +29045,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28181,6 +29186,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28317,6 +29327,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28453,6 +29468,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28589,6 +29609,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28725,6 +29750,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28861,6 +29891,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28997,6 +30032,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29133,6 +30173,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29269,6 +30314,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29405,6 +30455,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29541,6 +30596,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29677,6 +30737,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29813,6 +30878,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29949,6 +31019,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30085,6 +31160,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30221,6 +31301,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30357,6 +31442,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30493,6 +31583,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30629,6 +31724,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30765,6 +31865,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30901,6 +32006,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31037,6 +32147,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31173,6 +32288,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31318,6 +32438,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31454,6 +32579,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31590,6 +32720,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31726,6 +32861,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31862,6 +33002,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31998,6 +33143,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32134,6 +33284,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32270,6 +33425,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32406,6 +33566,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32542,6 +33707,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32678,6 +33848,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32814,6 +33989,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32950,6 +34130,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33086,6 +34271,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33222,6 +34412,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33358,6 +34553,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33494,6 +34694,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33630,6 +34835,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33766,6 +34976,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33902,6 +35117,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34038,6 +35258,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO246" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34174,6 +35399,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34310,6 +35540,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34446,6 +35681,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34582,6 +35822,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34718,6 +35963,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO251" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34852,6 +36102,11 @@
       <c r="S252" t="inlineStr">
         <is>
           <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO252" t="inlineStr">

--- a/diseases/d201/2026-2029.xlsx
+++ b/diseases/d201/2026-2029.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0.07936065154460033</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -788,22 +783,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -921,11 +906,6 @@
       <c r="R3" t="n">
         <v>0.1126387427714087</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -938,22 +918,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1062,11 +1032,6 @@
       <c r="R4" t="n">
         <v>0.03104502522097849</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1079,22 +1044,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1203,11 +1158,6 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1220,22 +1170,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1344,11 +1284,6 @@
       <c r="R6" t="n">
         <v>0.1234639540812862</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1361,22 +1296,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1485,11 +1410,6 @@
       <c r="R7" t="n">
         <v>0.06044539389979713</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1502,22 +1422,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1626,11 +1536,6 @@
       <c r="R8" t="n">
         <v>0.07525092690329213</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1643,22 +1548,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1767,11 +1662,6 @@
       <c r="R9" t="n">
         <v>0.06644527102361598</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1784,22 +1674,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1908,11 +1788,6 @@
       <c r="R10" t="n">
         <v>0.1204618410616832</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1925,22 +1800,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2049,11 +1914,6 @@
       <c r="R11" t="n">
         <v>0.01334216940739287</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2066,22 +1926,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2190,11 +2040,6 @@
       <c r="R12" t="n">
         <v>0.04270731947936361</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2207,22 +2052,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2331,11 +2166,6 @@
       <c r="R13" t="n">
         <v>0.09785505904364573</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2348,22 +2178,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2472,11 +2292,6 @@
       <c r="R14" t="n">
         <v>0.1018220374793344</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2489,22 +2304,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2613,11 +2418,6 @@
       <c r="R15" t="n">
         <v>0.02531434082722203</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2630,22 +2430,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2754,11 +2544,6 @@
       <c r="R16" t="n">
         <v>0.03426095242706871</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2771,22 +2556,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -2895,11 +2670,6 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2912,22 +2682,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3036,11 +2796,6 @@
       <c r="R18" t="n">
         <v>0.01043495392341746</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3053,22 +2808,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3177,11 +2922,6 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3194,22 +2934,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3318,11 +3048,6 @@
       <c r="R20" t="n">
         <v>0.1338637013179551</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3335,22 +3060,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3459,11 +3174,6 @@
       <c r="R21" t="n">
         <v>0.1044967870140682</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3476,22 +3186,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3600,11 +3300,6 @@
       <c r="R22" t="n">
         <v>0.05774110447762056</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3617,22 +3312,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3741,11 +3426,6 @@
       <c r="R23" t="n">
         <v>0.2276169979821753</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3758,22 +3438,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -3882,11 +3552,6 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3899,22 +3564,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4023,11 +3678,6 @@
       <c r="R25" t="n">
         <v>0.2136501622806514</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4040,22 +3690,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4164,11 +3804,6 @@
       <c r="R26" t="n">
         <v>0.01202970036783215</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4181,22 +3816,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4305,11 +3930,6 @@
       <c r="R27" t="n">
         <v>0.04334154655640577</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4322,22 +3942,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4446,11 +4056,6 @@
       <c r="R28" t="n">
         <v>0.0974468745625718</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4463,22 +4068,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4587,11 +4182,6 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4604,22 +4194,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4731,11 +4311,6 @@
       <c r="R30" t="n">
         <v>0.07329189583824854</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4748,22 +4323,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -4881,11 +4446,6 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4898,22 +4458,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5022,11 +4572,6 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5039,22 +4584,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5163,11 +4698,6 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5180,22 +4710,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5304,11 +4824,6 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5321,22 +4836,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5445,11 +4950,6 @@
       <c r="R35" t="n">
         <v>0.006716154877755235</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5462,22 +4962,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5586,11 +5076,6 @@
       <c r="R36" t="n">
         <v>0.03225039724426806</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5603,22 +5088,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -5727,11 +5202,6 @@
       <c r="R37" t="n">
         <v>0.03322263551180799</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5744,22 +5214,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -5868,11 +5328,6 @@
       <c r="R38" t="n">
         <v>0.07227710463700993</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5885,22 +5340,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6009,11 +5454,6 @@
       <c r="R39" t="n">
         <v>0.06671084703696434</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6026,22 +5466,12 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6150,11 +5580,6 @@
       <c r="R40" t="n">
         <v>0.01423577315978787</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6167,22 +5592,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6291,11 +5706,6 @@
       <c r="R41" t="n">
         <v>0.06989647074546124</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6308,22 +5718,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6432,11 +5832,6 @@
       <c r="R42" t="n">
         <v>0.03394067915977812</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6449,22 +5844,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6573,11 +5958,6 @@
       <c r="R43" t="n">
         <v>0.02531434082722203</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6590,22 +5970,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -6714,11 +6084,6 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6731,22 +6096,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -6855,11 +6210,6 @@
       <c r="R45" t="n">
         <v>0.04781454078436885</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6872,22 +6222,12 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -6996,11 +6336,6 @@
       <c r="R46" t="n">
         <v>0.05217476961708728</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7013,22 +6348,12 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7137,11 +6462,6 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7154,22 +6474,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7278,11 +6588,6 @@
       <c r="R48" t="n">
         <v>0.09203129465609411</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7295,22 +6600,12 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7419,11 +6714,6 @@
       <c r="R49" t="n">
         <v>0.08708065584505681</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7436,22 +6726,12 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -7560,11 +6840,6 @@
       <c r="R50" t="n">
         <v>0.202093865671672</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7577,22 +6852,12 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -7701,11 +6966,6 @@
       <c r="R51" t="n">
         <v>0.1138084989910877</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7718,22 +6978,12 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -7842,11 +7092,6 @@
       <c r="R52" t="n">
         <v>0.1314039726048998</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7859,22 +7104,12 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -7983,11 +7218,6 @@
       <c r="R53" t="n">
         <v>0.09792299104529856</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8000,22 +7230,12 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8124,11 +7344,6 @@
       <c r="R54" t="n">
         <v>0.01202970036783215</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8141,22 +7356,12 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8265,11 +7470,6 @@
       <c r="R55" t="n">
         <v>0.04334154655640577</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8282,22 +7482,12 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8406,11 +7596,6 @@
       <c r="R56" t="n">
         <v>0.138591110488991</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8423,22 +7608,12 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -8547,11 +7722,6 @@
       <c r="R57" t="n">
         <v>0.06265687715617979</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8564,22 +7734,12 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -8691,11 +7851,6 @@
       <c r="R58" t="n">
         <v>0.1741266060360937</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8708,22 +7863,12 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -8841,11 +7986,6 @@
       <c r="R59" t="n">
         <v>0.1126387427714087</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8858,22 +7998,12 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -8982,11 +8112,6 @@
       <c r="R60" t="n">
         <v>0.06209005044195698</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8999,22 +8124,12 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9123,11 +8238,6 @@
       <c r="R61" t="n">
         <v>0.0229309096279093</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9140,22 +8250,12 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9264,11 +8364,6 @@
       <c r="R62" t="n">
         <v>0.2469279081625724</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9281,22 +8376,12 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -9405,11 +8490,6 @@
       <c r="R63" t="n">
         <v>0.1477554073106152</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9422,22 +8502,12 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -9546,11 +8616,6 @@
       <c r="R64" t="n">
         <v>0.1720021186360963</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9563,22 +8628,12 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -9687,11 +8742,6 @@
       <c r="R65" t="n">
         <v>0.3986716261416959</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9704,22 +8754,12 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -9828,11 +8868,6 @@
       <c r="R66" t="n">
         <v>0.2409236821233664</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9845,22 +8880,12 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -9969,11 +8994,6 @@
       <c r="R67" t="n">
         <v>0.1467638634813216</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9986,22 +9006,12 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10110,11 +9120,6 @@
       <c r="R68" t="n">
         <v>0.04270731947936361</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10127,22 +9132,12 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -10251,11 +9246,6 @@
       <c r="R69" t="n">
         <v>0.1444527062072866</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10268,22 +9258,12 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -10392,11 +9372,6 @@
       <c r="R70" t="n">
         <v>0.1357627166391125</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10409,22 +9384,12 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -10533,11 +9498,6 @@
       <c r="R71" t="n">
         <v>0.02531434082722203</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10550,22 +9510,12 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -10674,11 +9624,6 @@
       <c r="R72" t="n">
         <v>0.07994222232982699</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10691,22 +9636,12 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -10815,11 +9750,6 @@
       <c r="R73" t="n">
         <v>0.1912581631374754</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10832,22 +9762,12 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -10956,11 +9876,6 @@
       <c r="R74" t="n">
         <v>0.1669592627746793</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10973,22 +9888,12 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -11097,11 +10002,6 @@
       <c r="R75" t="n">
         <v>0.02947577047453338</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11114,22 +10014,12 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -11238,11 +10128,6 @@
       <c r="R76" t="n">
         <v>0.3346592532948877</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11255,22 +10140,12 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -11379,11 +10254,6 @@
       <c r="R77" t="n">
         <v>0.1799666887464507</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11396,22 +10266,12 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -11520,11 +10380,6 @@
       <c r="R78" t="n">
         <v>0.2887055223881028</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11537,22 +10392,12 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -11661,11 +10506,6 @@
       <c r="R79" t="n">
         <v>0.05690424949554383</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11678,22 +10518,12 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -11802,11 +10632,6 @@
       <c r="R80" t="n">
         <v>0.2628079452097996</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11819,22 +10644,12 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -11943,11 +10758,6 @@
       <c r="R81" t="n">
         <v>0.2403564325657328</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11960,22 +10770,12 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -12084,11 +10884,6 @@
       <c r="R82" t="n">
         <v>0.02405940073566429</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12101,22 +10896,12 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -12225,11 +11010,6 @@
       <c r="R83" t="n">
         <v>0.1300246396692173</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12242,22 +11022,12 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -12366,11 +11136,6 @@
       <c r="R84" t="n">
         <v>0.2295415267473914</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12383,22 +11148,12 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -12507,11 +11262,6 @@
       <c r="R85" t="n">
         <v>0.1879706314685393</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12524,22 +11274,12 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -12648,11 +11388,6 @@
       <c r="R86" t="n">
         <v>0.08029430626865444</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12665,22 +11400,12 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -12798,11 +11523,6 @@
       <c r="R87" t="n">
         <v>0</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12815,22 +11535,12 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -12939,11 +11649,6 @@
       <c r="R88" t="n">
         <v>0</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12956,22 +11661,12 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -13080,11 +11775,6 @@
       <c r="R89" t="n">
         <v>0.1834472770232744</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13097,22 +11787,12 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -13221,11 +11901,6 @@
       <c r="R90" t="n">
         <v>0.1234639540812862</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13238,22 +11913,12 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -13362,11 +12027,6 @@
       <c r="R91" t="n">
         <v>0.06044539389979713</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13379,22 +12039,12 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -13503,11 +12153,6 @@
       <c r="R92" t="n">
         <v>0.07525092690329213</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13520,22 +12165,12 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -13644,11 +12279,6 @@
       <c r="R93" t="n">
         <v>0.2325584485826559</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13661,22 +12291,12 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -13785,11 +12405,6 @@
       <c r="R94" t="n">
         <v>0.04818473642467328</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13802,22 +12417,12 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -13926,11 +12531,6 @@
       <c r="R95" t="n">
         <v>0.1200795246665358</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13943,22 +12543,12 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -14067,11 +12657,6 @@
       <c r="R96" t="n">
         <v>0.04270731947936361</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14084,22 +12669,12 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -14208,11 +12783,6 @@
       <c r="R97" t="n">
         <v>0.0792160001781894</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14225,22 +12795,12 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -14349,11 +12909,6 @@
       <c r="R98" t="n">
         <v>0.1357627166391125</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14366,22 +12921,12 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -14490,11 +13035,6 @@
       <c r="R99" t="n">
         <v>0.05062868165444406</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14507,22 +13047,12 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
         <v>0</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -14631,11 +13161,6 @@
       <c r="R100" t="n">
         <v>0.06852190485413742</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14648,22 +13173,12 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
-      </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -14772,11 +13287,6 @@
       <c r="R101" t="n">
         <v>0.04781454078436885</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14789,22 +13299,12 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
-      </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -14913,11 +13413,6 @@
       <c r="R102" t="n">
         <v>0.06260972354050473</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14930,22 +13425,12 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
-      </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -15054,11 +13539,6 @@
       <c r="R103" t="n">
         <v>0.02947577047453338</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15071,22 +13551,12 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
         <v>0</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -15195,11 +13665,6 @@
       <c r="R104" t="n">
         <v>0.1087642573208385</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15212,22 +13677,12 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -15336,11 +13791,6 @@
       <c r="R105" t="n">
         <v>0.3018796069295303</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15353,22 +13803,12 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -15477,11 +13917,6 @@
       <c r="R106" t="n">
         <v>0.1154822089552411</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15494,22 +13929,12 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
-      </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -15618,11 +14043,6 @@
       <c r="R107" t="n">
         <v>0.2276169979821753</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15635,22 +14055,12 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -15759,11 +14169,6 @@
       <c r="R108" t="n">
         <v>0</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15776,22 +14181,12 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
-      </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -15900,11 +14295,6 @@
       <c r="R109" t="n">
         <v>0.2314543424707056</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15917,22 +14307,12 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -16041,11 +14421,6 @@
       <c r="R110" t="n">
         <v>0.02405940073566429</v>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16058,22 +14433,12 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -16182,11 +14547,6 @@
       <c r="R111" t="n">
         <v>0</v>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16199,22 +14559,12 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
-      </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -16323,11 +14673,6 @@
       <c r="R112" t="n">
         <v>0.1667424298070673</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16340,22 +14685,12 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -16464,11 +14799,6 @@
       <c r="R113" t="n">
         <v>0.1253137543123596</v>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16481,22 +14811,12 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
-      </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -16605,11 +14925,6 @@
       <c r="R114" t="n">
         <v>0.0004668273620270607</v>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16622,22 +14937,12 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
         <v>0</v>
-      </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -16755,11 +15060,6 @@
       <c r="R115" t="n">
         <v>0.1126387427714087</v>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16772,22 +15072,12 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
         <v>0</v>
-      </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -16896,11 +15186,6 @@
       <c r="R116" t="n">
         <v>0</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16913,22 +15198,12 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -17037,11 +15312,6 @@
       <c r="R117" t="n">
         <v>0.04586181925581861</v>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17054,22 +15324,12 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
-      </c>
-      <c r="AU117" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -17178,11 +15438,6 @@
       <c r="R118" t="n">
         <v>0.1234639540812862</v>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17195,22 +15450,12 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
         <v>0</v>
-      </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -17319,11 +15564,6 @@
       <c r="R119" t="n">
         <v>0.02686461951102094</v>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17336,22 +15576,12 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
         <v>0</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -17460,11 +15690,6 @@
       <c r="R120" t="n">
         <v>0.08600105931804815</v>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17477,22 +15702,12 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
-      </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -17601,11 +15816,6 @@
       <c r="R121" t="n">
         <v>0.09966790653542397</v>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17618,22 +15828,12 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
         <v>0</v>
-      </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -17742,11 +15942,6 @@
       <c r="R122" t="n">
         <v>0.07227710463700993</v>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17759,22 +15954,12 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
-      </c>
-      <c r="AU122" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -17883,11 +16068,6 @@
       <c r="R123" t="n">
         <v>0.01334216940739287</v>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17900,22 +16080,12 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
         <v>0</v>
-      </c>
-      <c r="AU123" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
@@ -18024,11 +16194,6 @@
       <c r="R124" t="n">
         <v>0.02847154631957574</v>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18041,22 +16206,12 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -18165,11 +16320,6 @@
       <c r="R125" t="n">
         <v>0.08387576489455348</v>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18182,22 +16332,12 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
-      </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -18306,11 +16446,6 @@
       <c r="R126" t="n">
         <v>0</v>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18323,22 +16458,12 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
         <v>0</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -18447,11 +16572,6 @@
       <c r="R127" t="n">
         <v>0.05062868165444406</v>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18464,22 +16584,12 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
         <v>0</v>
-      </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
@@ -18588,11 +16698,6 @@
       <c r="R128" t="n">
         <v>0.03426095242706871</v>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18605,22 +16710,12 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
         <v>0</v>
-      </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
@@ -18729,11 +16824,6 @@
       <c r="R129" t="n">
         <v>0.0956290815687377</v>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18746,22 +16836,12 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
         <v>0</v>
-      </c>
-      <c r="AU129" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
@@ -18870,11 +16950,6 @@
       <c r="R130" t="n">
         <v>0.1043495392341746</v>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18887,22 +16962,12 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr"/>
       <c r="AT130" t="n">
         <v>0</v>
-      </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
@@ -19011,11 +17076,6 @@
       <c r="R131" t="n">
         <v>0.02947577047453338</v>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19028,22 +17088,12 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
         <v>0</v>
-      </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
@@ -19152,11 +17202,6 @@
       <c r="R132" t="n">
         <v>0.1422301826503273</v>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19169,22 +17214,12 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr"/>
       <c r="AT132" t="n">
         <v>0</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
@@ -19293,11 +17328,6 @@
       <c r="R133" t="n">
         <v>0.3076849839858674</v>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19310,22 +17340,12 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
         <v>0</v>
-      </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
@@ -19434,11 +17454,6 @@
       <c r="R134" t="n">
         <v>0.1154822089552411</v>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19451,22 +17466,12 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
         <v>0</v>
-      </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
@@ -19575,11 +17580,6 @@
       <c r="R135" t="n">
         <v>0</v>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19592,22 +17592,12 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
         <v>0</v>
-      </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
@@ -19716,11 +17706,6 @@
       <c r="R136" t="n">
         <v>0.2628079452097996</v>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19733,22 +17718,12 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
         <v>0</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
@@ -19857,11 +17832,6 @@
       <c r="R137" t="n">
         <v>0.05341254057016284</v>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19874,22 +17844,12 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
         <v>0</v>
-      </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
@@ -19998,11 +17958,6 @@
       <c r="R138" t="n">
         <v>0</v>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20015,22 +17970,12 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
         <v>0</v>
-      </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
@@ -20139,11 +18084,6 @@
       <c r="R139" t="n">
         <v>0.04334154655640577</v>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20156,22 +18096,12 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
         <v>0</v>
-      </c>
-      <c r="AU139" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
@@ -20280,11 +18210,6 @@
       <c r="R140" t="n">
         <v>0.1407565965903815</v>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20297,22 +18222,12 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
         <v>0</v>
-      </c>
-      <c r="AU140" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
@@ -20421,11 +18336,6 @@
       <c r="R141" t="n">
         <v>0.06265687715617979</v>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20438,22 +18348,12 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
         <v>0</v>
-      </c>
-      <c r="AU141" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
@@ -20562,11 +18462,6 @@
       <c r="R142" t="n">
         <v>0</v>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20579,22 +18474,12 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
         <v>0</v>
-      </c>
-      <c r="AU142" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
@@ -20703,11 +18588,6 @@
       <c r="R143" t="n">
         <v>0</v>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20720,22 +18600,12 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
         <v>0</v>
-      </c>
-      <c r="AU143" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
@@ -20844,11 +18714,6 @@
       <c r="R144" t="n">
         <v>0.06879272888372791</v>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20861,22 +18726,12 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
         <v>0</v>
-      </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
@@ -20985,11 +18840,6 @@
       <c r="R145" t="n">
         <v>0.1234639540812862</v>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21002,22 +18852,12 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
-      </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -21126,11 +18966,6 @@
       <c r="R146" t="n">
         <v>0.02014846463326571</v>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21143,22 +18978,12 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="n">
         <v>0</v>
-      </c>
-      <c r="AU146" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
@@ -21267,11 +19092,6 @@
       <c r="R147" t="n">
         <v>0.01075013241475602</v>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21284,22 +19104,12 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
         <v>0</v>
-      </c>
-      <c r="AU147" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
@@ -21408,11 +19218,6 @@
       <c r="R148" t="n">
         <v>0.06644527102361598</v>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21425,22 +19230,12 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
         <v>0</v>
-      </c>
-      <c r="AU148" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
@@ -21549,11 +19344,6 @@
       <c r="R149" t="n">
         <v>0.04818473642467328</v>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21566,22 +19356,12 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
         <v>0</v>
-      </c>
-      <c r="AU149" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
@@ -21690,11 +19470,6 @@
       <c r="R150" t="n">
         <v>0.05336867762957147</v>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21707,22 +19482,12 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
         <v>0</v>
-      </c>
-      <c r="AU150" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
@@ -21831,11 +19596,6 @@
       <c r="R151" t="n">
         <v>0.04270731947936361</v>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21848,22 +19608,12 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="n">
         <v>0</v>
-      </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
@@ -21972,11 +19722,6 @@
       <c r="R152" t="n">
         <v>0.0792160001781894</v>
       </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21989,22 +19734,12 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr"/>
       <c r="AT152" t="n">
         <v>0</v>
-      </c>
-      <c r="AU152" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
@@ -22113,11 +19848,6 @@
       <c r="R153" t="n">
         <v>0.1018220374793344</v>
       </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22130,22 +19860,12 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR153" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
         <v>0</v>
-      </c>
-      <c r="AU153" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
@@ -22254,11 +19974,6 @@
       <c r="R154" t="n">
         <v>0</v>
       </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22271,22 +19986,12 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR154" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
         <v>0</v>
-      </c>
-      <c r="AU154" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
@@ -22395,11 +20100,6 @@
       <c r="R155" t="n">
         <v>0.01142031747568957</v>
       </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22412,22 +20112,12 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR155" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
-      </c>
-      <c r="AU155" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
@@ -22536,11 +20226,6 @@
       <c r="R156" t="n">
         <v>0</v>
       </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22553,22 +20238,12 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR156" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
         <v>0</v>
-      </c>
-      <c r="AU156" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
@@ -22677,11 +20352,6 @@
       <c r="R157" t="n">
         <v>0.07304467746392218</v>
       </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22694,22 +20364,12 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
         <v>0</v>
-      </c>
-      <c r="AU157" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
@@ -22818,11 +20478,6 @@
       <c r="R158" t="n">
         <v>0.02947577047453338</v>
       </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22835,22 +20490,12 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
         <v>0</v>
-      </c>
-      <c r="AU158" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -22959,11 +20604,6 @@
       <c r="R159" t="n">
         <v>0.1087642573208385</v>
       </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22976,22 +20616,12 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr"/>
       <c r="AT159" t="n">
         <v>0</v>
-      </c>
-      <c r="AU159" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
@@ -23100,11 +20730,6 @@
       <c r="R160" t="n">
         <v>0.4063763939435984</v>
       </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23117,22 +20742,12 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
         <v>0</v>
-      </c>
-      <c r="AU160" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
@@ -23241,11 +20856,6 @@
       <c r="R161" t="n">
         <v>0.02887055223881028</v>
       </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23258,22 +20868,12 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
         <v>0</v>
-      </c>
-      <c r="AU161" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
@@ -23382,11 +20982,6 @@
       <c r="R162" t="n">
         <v>0.1138084989910877</v>
       </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23399,22 +20994,12 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
         <v>0</v>
-      </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
@@ -23523,11 +21108,6 @@
       <c r="R163" t="n">
         <v>0.1314039726048998</v>
       </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23540,22 +21120,12 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
         <v>0</v>
-      </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
@@ -23664,11 +21234,6 @@
       <c r="R164" t="n">
         <v>0.06231463066518999</v>
       </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23681,22 +21246,12 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr"/>
       <c r="AT164" t="n">
         <v>0</v>
-      </c>
-      <c r="AU164" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
@@ -23805,11 +21360,6 @@
       <c r="R165" t="n">
         <v>0.01202970036783215</v>
       </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23822,22 +21372,12 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
         <v>0</v>
-      </c>
-      <c r="AU165" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
@@ -23946,11 +21486,6 @@
       <c r="R166" t="n">
         <v>0</v>
       </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23963,22 +21498,12 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
         <v>0</v>
-      </c>
-      <c r="AU166" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
@@ -24087,11 +21612,6 @@
       <c r="R167" t="n">
         <v>0.1948937491251436</v>
       </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24104,22 +21624,12 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
         <v>0</v>
-      </c>
-      <c r="AU167" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
@@ -24228,11 +21738,6 @@
       <c r="R168" t="n">
         <v>0.1253137543123596</v>
       </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24245,22 +21750,12 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR168" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
         <v>0</v>
-      </c>
-      <c r="AU168" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
@@ -24369,11 +21864,6 @@
       <c r="R169" t="n">
         <v>0.2049372119298797</v>
       </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24386,22 +21876,12 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR169" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
         <v>0</v>
-      </c>
-      <c r="AU169" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
@@ -24519,11 +21999,6 @@
       <c r="R170" t="n">
         <v>0</v>
       </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24536,22 +22011,12 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr"/>
       <c r="AT170" t="n">
         <v>0</v>
-      </c>
-      <c r="AU170" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
@@ -24660,11 +22125,6 @@
       <c r="R171" t="n">
         <v>0</v>
       </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24677,22 +22137,12 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR171" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
         <v>0</v>
-      </c>
-      <c r="AU171" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
@@ -24801,11 +22251,6 @@
       <c r="R172" t="n">
         <v>0.0229309096279093</v>
       </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24818,22 +22263,12 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr"/>
       <c r="AT172" t="n">
         <v>0</v>
-      </c>
-      <c r="AU172" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
@@ -24942,11 +22377,6 @@
       <c r="R173" t="n">
         <v>0.2469279081625724</v>
       </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24959,22 +22389,12 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr"/>
       <c r="AT173" t="n">
         <v>0</v>
-      </c>
-      <c r="AU173" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
@@ -25083,11 +22503,6 @@
       <c r="R174" t="n">
         <v>0.02686461951102094</v>
       </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25100,22 +22515,12 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR174" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
         <v>0</v>
-      </c>
-      <c r="AU174" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
@@ -25224,11 +22629,6 @@
       <c r="R175" t="n">
         <v>0.03225039724426806</v>
       </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25241,22 +22641,12 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR175" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr"/>
       <c r="AT175" t="n">
         <v>0</v>
-      </c>
-      <c r="AU175" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
@@ -25365,11 +22755,6 @@
       <c r="R176" t="n">
         <v>0.03322263551180799</v>
       </c>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25382,22 +22767,12 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR176" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr"/>
       <c r="AT176" t="n">
         <v>0</v>
-      </c>
-      <c r="AU176" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
@@ -25506,11 +22881,6 @@
       <c r="R177" t="n">
         <v>0.337293154972713</v>
       </c>
-      <c r="S177" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25523,22 +22893,12 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR177" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
         <v>0</v>
-      </c>
-      <c r="AU177" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
@@ -25647,11 +23007,6 @@
       <c r="R178" t="n">
         <v>0.1067373552591429</v>
       </c>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25664,22 +23019,12 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR178" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS178" t="inlineStr"/>
       <c r="AT178" t="n">
         <v>0</v>
-      </c>
-      <c r="AU178" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
@@ -25788,11 +23133,6 @@
       <c r="R179" t="n">
         <v>0.01423577315978787</v>
       </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25805,22 +23145,12 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR179" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr"/>
       <c r="AT179" t="n">
         <v>0</v>
-      </c>
-      <c r="AU179" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
@@ -25929,11 +23259,6 @@
       <c r="R180" t="n">
         <v>0.1164941179091021</v>
       </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25946,22 +23271,12 @@
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR180" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
         <v>0</v>
-      </c>
-      <c r="AU180" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
@@ -26070,11 +23385,6 @@
       <c r="R181" t="n">
         <v>0.06788135831955625</v>
       </c>
-      <c r="S181" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26087,22 +23397,12 @@
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR181" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS181" t="inlineStr"/>
       <c r="AT181" t="n">
         <v>0</v>
-      </c>
-      <c r="AU181" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
@@ -26211,11 +23511,6 @@
       <c r="R182" t="n">
         <v>0.02531434082722203</v>
       </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26228,22 +23523,12 @@
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR182" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS182" t="inlineStr"/>
       <c r="AT182" t="n">
         <v>0</v>
-      </c>
-      <c r="AU182" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
@@ -26352,11 +23637,6 @@
       <c r="R183" t="n">
         <v>0.04568126990275828</v>
       </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26369,22 +23649,12 @@
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR183" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS183" t="inlineStr"/>
       <c r="AT183" t="n">
         <v>0</v>
-      </c>
-      <c r="AU183" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
@@ -26493,11 +23763,6 @@
       <c r="R184" t="n">
         <v>0.04781454078436885</v>
       </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26510,22 +23775,12 @@
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR184" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS184" t="inlineStr"/>
       <c r="AT184" t="n">
         <v>0</v>
-      </c>
-      <c r="AU184" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
@@ -26634,11 +23889,6 @@
       <c r="R185" t="n">
         <v>0.1252194470810095</v>
       </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26651,22 +23901,12 @@
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR185" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS185" t="inlineStr"/>
       <c r="AT185" t="n">
         <v>0</v>
-      </c>
-      <c r="AU185" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
@@ -26775,11 +24015,6 @@
       <c r="R186" t="n">
         <v>0.02947577047453338</v>
       </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26792,22 +24027,12 @@
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR186" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr"/>
       <c r="AT186" t="n">
         <v>0</v>
-      </c>
-      <c r="AU186" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
@@ -26916,11 +24141,6 @@
       <c r="R187" t="n">
         <v>0.1505966639826994</v>
       </c>
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26933,22 +24153,12 @@
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR187" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS187" t="inlineStr"/>
       <c r="AT187" t="n">
         <v>0</v>
-      </c>
-      <c r="AU187" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
@@ -27057,11 +24267,6 @@
       <c r="R188" t="n">
         <v>0.2786580987041818</v>
       </c>
-      <c r="S188" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27074,22 +24279,12 @@
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR188" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS188" t="inlineStr"/>
       <c r="AT188" t="n">
         <v>0</v>
-      </c>
-      <c r="AU188" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
@@ -27198,11 +24393,6 @@
       <c r="R189" t="n">
         <v>0.202093865671672</v>
       </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27215,22 +24405,12 @@
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR189" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS189" t="inlineStr"/>
       <c r="AT189" t="n">
         <v>0</v>
-      </c>
-      <c r="AU189" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
@@ -27339,11 +24519,6 @@
       <c r="R190" t="n">
         <v>0</v>
       </c>
-      <c r="S190" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27356,22 +24531,12 @@
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR190" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS190" t="inlineStr"/>
       <c r="AT190" t="n">
         <v>0</v>
-      </c>
-      <c r="AU190" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
@@ -27480,11 +24645,6 @@
       <c r="R191" t="n">
         <v>0.1314039726048998</v>
       </c>
-      <c r="S191" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27497,22 +24657,12 @@
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR191" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS191" t="inlineStr"/>
       <c r="AT191" t="n">
         <v>0</v>
-      </c>
-      <c r="AU191" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
@@ -27621,11 +24771,6 @@
       <c r="R192" t="n">
         <v>0.0890209009502714</v>
       </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27638,22 +24783,12 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR192" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr"/>
       <c r="AT192" t="n">
         <v>0</v>
-      </c>
-      <c r="AU192" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
@@ -27762,11 +24897,6 @@
       <c r="R193" t="n">
         <v>0.02405940073566429</v>
       </c>
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27779,22 +24909,12 @@
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR193" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS193" t="inlineStr"/>
       <c r="AT193" t="n">
         <v>0</v>
-      </c>
-      <c r="AU193" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
@@ -27903,11 +25023,6 @@
       <c r="R194" t="n">
         <v>0</v>
       </c>
-      <c r="S194" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27920,22 +25035,12 @@
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR194" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS194" t="inlineStr"/>
       <c r="AT194" t="n">
         <v>0</v>
-      </c>
-      <c r="AU194" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
@@ -28044,11 +25149,6 @@
       <c r="R195" t="n">
         <v>0.5868467334768214</v>
       </c>
-      <c r="S195" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28061,22 +25161,12 @@
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR195" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS195" t="inlineStr"/>
       <c r="AT195" t="n">
         <v>0</v>
-      </c>
-      <c r="AU195" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
@@ -28185,11 +25275,6 @@
       <c r="R196" t="n">
         <v>0.06265687715617979</v>
       </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28202,22 +25287,12 @@
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR196" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS196" t="inlineStr"/>
       <c r="AT196" t="n">
         <v>0</v>
-      </c>
-      <c r="AU196" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
@@ -28326,11 +25401,6 @@
       <c r="R197" t="n">
         <v>0.9541951279833122</v>
       </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28343,22 +25413,12 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR197" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS197" t="inlineStr"/>
       <c r="AT197" t="n">
         <v>0</v>
-      </c>
-      <c r="AU197" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
@@ -28476,11 +25536,6 @@
       <c r="R198" t="n">
         <v>0</v>
       </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28493,22 +25548,12 @@
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR198" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS198" t="inlineStr"/>
       <c r="AT198" t="n">
         <v>0</v>
-      </c>
-      <c r="AU198" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
@@ -28617,11 +25662,6 @@
       <c r="R199" t="n">
         <v>0.09313507566293547</v>
       </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28634,22 +25674,12 @@
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR199" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS199" t="inlineStr"/>
       <c r="AT199" t="n">
         <v>0</v>
-      </c>
-      <c r="AU199" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
@@ -28758,11 +25788,6 @@
       <c r="R200" t="n">
         <v>0.2063781866511837</v>
       </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28775,22 +25800,12 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR200" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr"/>
       <c r="AT200" t="n">
         <v>0</v>
-      </c>
-      <c r="AU200" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
@@ -28899,11 +25914,6 @@
       <c r="R201" t="n">
         <v>0</v>
       </c>
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28916,22 +25926,12 @@
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR201" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS201" t="inlineStr"/>
       <c r="AT201" t="n">
         <v>0</v>
-      </c>
-      <c r="AU201" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
@@ -29040,11 +26040,6 @@
       <c r="R202" t="n">
         <v>0.1343230975551047</v>
       </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29057,22 +26052,12 @@
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR202" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS202" t="inlineStr"/>
       <c r="AT202" t="n">
         <v>0</v>
-      </c>
-      <c r="AU202" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
@@ -29181,11 +26166,6 @@
       <c r="R203" t="n">
         <v>0.07525092690329213</v>
       </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29198,22 +26178,12 @@
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR203" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS203" t="inlineStr"/>
       <c r="AT203" t="n">
         <v>0</v>
-      </c>
-      <c r="AU203" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
@@ -29322,11 +26292,6 @@
       <c r="R204" t="n">
         <v>0.132890542047232</v>
       </c>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29339,22 +26304,12 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR204" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS204" t="inlineStr"/>
       <c r="AT204" t="n">
         <v>0</v>
-      </c>
-      <c r="AU204" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
@@ -29463,11 +26418,6 @@
       <c r="R205" t="n">
         <v>0.2168313139110298</v>
       </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29480,22 +26430,12 @@
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR205" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS205" t="inlineStr"/>
       <c r="AT205" t="n">
         <v>0</v>
-      </c>
-      <c r="AU205" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
@@ -29604,11 +26544,6 @@
       <c r="R206" t="n">
         <v>0.2401590493330717</v>
       </c>
-      <c r="S206" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29621,22 +26556,12 @@
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR206" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS206" t="inlineStr"/>
       <c r="AT206" t="n">
         <v>0</v>
-      </c>
-      <c r="AU206" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
@@ -29745,11 +26670,6 @@
       <c r="R207" t="n">
         <v>0.02847154631957574</v>
       </c>
-      <c r="S207" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29762,22 +26682,12 @@
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR207" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS207" t="inlineStr"/>
       <c r="AT207" t="n">
         <v>0</v>
-      </c>
-      <c r="AU207" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
@@ -29886,11 +26796,6 @@
       <c r="R208" t="n">
         <v>0.1584320003563788</v>
       </c>
-      <c r="S208" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29903,22 +26808,12 @@
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR208" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS208" t="inlineStr"/>
       <c r="AT208" t="n">
         <v>0</v>
-      </c>
-      <c r="AU208" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
@@ -30027,11 +26922,6 @@
       <c r="R209" t="n">
         <v>0.03394067915977812</v>
       </c>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30044,22 +26934,12 @@
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR209" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS209" t="inlineStr"/>
       <c r="AT209" t="n">
         <v>0</v>
-      </c>
-      <c r="AU209" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
@@ -30168,11 +27048,6 @@
       <c r="R210" t="n">
         <v>0.1772003857905542</v>
       </c>
-      <c r="S210" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30185,22 +27060,12 @@
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR210" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS210" t="inlineStr"/>
       <c r="AT210" t="n">
         <v>0</v>
-      </c>
-      <c r="AU210" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
@@ -30309,11 +27174,6 @@
       <c r="R211" t="n">
         <v>0.159884444659654</v>
       </c>
-      <c r="S211" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30326,22 +27186,12 @@
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR211" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS211" t="inlineStr"/>
       <c r="AT211" t="n">
         <v>0</v>
-      </c>
-      <c r="AU211" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
@@ -30450,11 +27300,6 @@
       <c r="R212" t="n">
         <v>0.1434436223531065</v>
       </c>
-      <c r="S212" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30467,22 +27312,12 @@
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR212" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS212" t="inlineStr"/>
       <c r="AT212" t="n">
         <v>0</v>
-      </c>
-      <c r="AU212" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
@@ -30591,11 +27426,6 @@
       <c r="R213" t="n">
         <v>0.1669592627746793</v>
       </c>
-      <c r="S213" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA213" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30608,22 +27438,12 @@
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR213" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS213" t="inlineStr"/>
       <c r="AT213" t="n">
         <v>0</v>
-      </c>
-      <c r="AU213" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
@@ -30732,11 +27552,6 @@
       <c r="R214" t="n">
         <v>0</v>
       </c>
-      <c r="S214" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA214" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30749,22 +27564,12 @@
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR214" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS214" t="inlineStr"/>
       <c r="AT214" t="n">
         <v>0</v>
-      </c>
-      <c r="AU214" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
@@ -30873,11 +27678,6 @@
       <c r="R215" t="n">
         <v>0.3262927719625155</v>
       </c>
-      <c r="S215" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA215" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30890,22 +27690,12 @@
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR215" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS215" t="inlineStr"/>
       <c r="AT215" t="n">
         <v>0</v>
-      </c>
-      <c r="AU215" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
@@ -31014,11 +27804,6 @@
       <c r="R216" t="n">
         <v>0.3309064922112159</v>
       </c>
-      <c r="S216" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31031,22 +27816,12 @@
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR216" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS216" t="inlineStr"/>
       <c r="AT216" t="n">
         <v>0</v>
-      </c>
-      <c r="AU216" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
@@ -31155,11 +27930,6 @@
       <c r="R217" t="n">
         <v>0.202093865671672</v>
       </c>
-      <c r="S217" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA217" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31172,22 +27942,12 @@
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR217" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS217" t="inlineStr"/>
       <c r="AT217" t="n">
         <v>0</v>
-      </c>
-      <c r="AU217" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
@@ -31296,11 +28056,6 @@
       <c r="R218" t="n">
         <v>0.05690424949554383</v>
       </c>
-      <c r="S218" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA218" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31313,22 +28068,12 @@
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR218" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS218" t="inlineStr"/>
       <c r="AT218" t="n">
         <v>0</v>
-      </c>
-      <c r="AU218" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
@@ -31437,11 +28182,6 @@
       <c r="R219" t="n">
         <v>0.1314039726048998</v>
       </c>
-      <c r="S219" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA219" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31454,22 +28194,12 @@
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR219" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS219" t="inlineStr"/>
       <c r="AT219" t="n">
         <v>0</v>
-      </c>
-      <c r="AU219" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
@@ -31578,11 +28308,6 @@
       <c r="R220" t="n">
         <v>0.2403564325657328</v>
       </c>
-      <c r="S220" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA220" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31595,22 +28320,12 @@
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR220" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS220" t="inlineStr"/>
       <c r="AT220" t="n">
         <v>0</v>
-      </c>
-      <c r="AU220" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
@@ -31719,11 +28434,6 @@
       <c r="R221" t="n">
         <v>0.01202970036783215</v>
       </c>
-      <c r="S221" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31736,22 +28446,12 @@
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR221" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS221" t="inlineStr"/>
       <c r="AT221" t="n">
         <v>0</v>
-      </c>
-      <c r="AU221" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
@@ -31860,11 +28560,6 @@
       <c r="R222" t="n">
         <v>0.2600492793384346</v>
       </c>
-      <c r="S222" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA222" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31877,22 +28572,12 @@
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR222" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr"/>
       <c r="AT222" t="n">
         <v>0</v>
-      </c>
-      <c r="AU222" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
@@ -32001,11 +28686,6 @@
       <c r="R223" t="n">
         <v>3.8004281079403</v>
       </c>
-      <c r="S223" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA223" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32018,22 +28698,12 @@
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR223" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr"/>
       <c r="AT223" t="n">
         <v>0</v>
-      </c>
-      <c r="AU223" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
@@ -32142,11 +28812,6 @@
       <c r="R224" t="n">
         <v>0</v>
       </c>
-      <c r="S224" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32159,22 +28824,12 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR224" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr"/>
       <c r="AT224" t="n">
         <v>0</v>
-      </c>
-      <c r="AU224" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
@@ -32283,11 +28938,6 @@
       <c r="R225" t="n">
         <v>0.1349131076258205</v>
       </c>
-      <c r="S225" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA225" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32300,22 +28950,12 @@
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR225" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS225" t="inlineStr"/>
       <c r="AT225" t="n">
         <v>0</v>
-      </c>
-      <c r="AU225" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
@@ -32433,11 +29073,6 @@
       <c r="R226" t="n">
         <v>0</v>
       </c>
-      <c r="S226" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA226" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32450,22 +29085,12 @@
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR226" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS226" t="inlineStr"/>
       <c r="AT226" t="n">
         <v>0</v>
-      </c>
-      <c r="AU226" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
@@ -32574,11 +29199,6 @@
       <c r="R227" t="n">
         <v>0.03104502522097849</v>
       </c>
-      <c r="S227" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA227" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32591,22 +29211,12 @@
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR227" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS227" t="inlineStr"/>
       <c r="AT227" t="n">
         <v>0</v>
-      </c>
-      <c r="AU227" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
@@ -32715,11 +29325,6 @@
       <c r="R228" t="n">
         <v>0.1146545481395465</v>
       </c>
-      <c r="S228" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA228" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32732,22 +29337,12 @@
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR228" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS228" t="inlineStr"/>
       <c r="AT228" t="n">
         <v>0</v>
-      </c>
-      <c r="AU228" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
@@ -32856,11 +29451,6 @@
       <c r="R229" t="n">
         <v>0</v>
       </c>
-      <c r="S229" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA229" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32873,22 +29463,12 @@
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR229" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS229" t="inlineStr"/>
       <c r="AT229" t="n">
         <v>0</v>
-      </c>
-      <c r="AU229" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
@@ -32997,11 +29577,6 @@
       <c r="R230" t="n">
         <v>0.01343230975551047</v>
       </c>
-      <c r="S230" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA230" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33014,22 +29589,12 @@
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR230" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS230" t="inlineStr"/>
       <c r="AT230" t="n">
         <v>0</v>
-      </c>
-      <c r="AU230" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
@@ -33138,11 +29703,6 @@
       <c r="R231" t="n">
         <v>0</v>
       </c>
-      <c r="S231" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA231" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33155,22 +29715,12 @@
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR231" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS231" t="inlineStr"/>
       <c r="AT231" t="n">
         <v>0</v>
-      </c>
-      <c r="AU231" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
@@ -33279,11 +29829,6 @@
       <c r="R232" t="n">
         <v>0</v>
       </c>
-      <c r="S232" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA232" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33296,22 +29841,12 @@
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR232" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS232" t="inlineStr"/>
       <c r="AT232" t="n">
         <v>0</v>
-      </c>
-      <c r="AU232" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
@@ -33420,11 +29955,6 @@
       <c r="R233" t="n">
         <v>0.5541244688837428</v>
       </c>
-      <c r="S233" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA233" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33437,22 +29967,12 @@
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR233" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS233" t="inlineStr"/>
       <c r="AT233" t="n">
         <v>0</v>
-      </c>
-      <c r="AU233" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
@@ -33561,11 +30081,6 @@
       <c r="R234" t="n">
         <v>0.09339518585175008</v>
       </c>
-      <c r="S234" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA234" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33578,22 +30093,12 @@
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR234" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS234" t="inlineStr"/>
       <c r="AT234" t="n">
         <v>0</v>
-      </c>
-      <c r="AU234" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
@@ -33702,11 +30207,6 @@
       <c r="R235" t="n">
         <v>0</v>
       </c>
-      <c r="S235" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA235" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33719,22 +30219,12 @@
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR235" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS235" t="inlineStr"/>
       <c r="AT235" t="n">
         <v>0</v>
-      </c>
-      <c r="AU235" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
@@ -33843,11 +30333,6 @@
       <c r="R236" t="n">
         <v>0.01863905886545633</v>
       </c>
-      <c r="S236" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA236" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33860,22 +30345,12 @@
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR236" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS236" t="inlineStr"/>
       <c r="AT236" t="n">
         <v>0</v>
-      </c>
-      <c r="AU236" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
@@ -33984,11 +30459,6 @@
       <c r="R237" t="n">
         <v>0</v>
       </c>
-      <c r="S237" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA237" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34001,22 +30471,12 @@
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR237" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS237" t="inlineStr"/>
       <c r="AT237" t="n">
         <v>0</v>
-      </c>
-      <c r="AU237" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
@@ -34125,11 +30585,6 @@
       <c r="R238" t="n">
         <v>0</v>
       </c>
-      <c r="S238" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA238" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34142,22 +30597,12 @@
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR238" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS238" t="inlineStr"/>
       <c r="AT238" t="n">
         <v>0</v>
-      </c>
-      <c r="AU238" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
@@ -34266,11 +30711,6 @@
       <c r="R239" t="n">
         <v>0.01142031747568957</v>
       </c>
-      <c r="S239" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA239" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34283,22 +30723,12 @@
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR239" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS239" t="inlineStr"/>
       <c r="AT239" t="n">
         <v>0</v>
-      </c>
-      <c r="AU239" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
@@ -34407,11 +30837,6 @@
       <c r="R240" t="n">
         <v>0</v>
       </c>
-      <c r="S240" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA240" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34424,22 +30849,12 @@
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR240" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS240" t="inlineStr"/>
       <c r="AT240" t="n">
         <v>0</v>
-      </c>
-      <c r="AU240" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
@@ -34548,11 +30963,6 @@
       <c r="R241" t="n">
         <v>0.03130486177025237</v>
       </c>
-      <c r="S241" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34565,22 +30975,12 @@
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR241" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS241" t="inlineStr"/>
       <c r="AT241" t="n">
         <v>0</v>
-      </c>
-      <c r="AU241" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
@@ -34689,11 +31089,6 @@
       <c r="R242" t="n">
         <v>0</v>
       </c>
-      <c r="S242" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA242" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34706,22 +31101,12 @@
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR242" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS242" t="inlineStr"/>
       <c r="AT242" t="n">
         <v>0</v>
-      </c>
-      <c r="AU242" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
@@ -34830,11 +31215,6 @@
       <c r="R243" t="n">
         <v>0.04183240666186096</v>
       </c>
-      <c r="S243" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA243" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34847,22 +31227,12 @@
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR243" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS243" t="inlineStr"/>
       <c r="AT243" t="n">
         <v>0</v>
-      </c>
-      <c r="AU243" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
@@ -34971,11 +31341,6 @@
       <c r="R244" t="n">
         <v>0.03483226233802272</v>
       </c>
-      <c r="S244" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA244" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34988,22 +31353,12 @@
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR244" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS244" t="inlineStr"/>
       <c r="AT244" t="n">
         <v>0</v>
-      </c>
-      <c r="AU244" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
@@ -35112,11 +31467,6 @@
       <c r="R245" t="n">
         <v>0</v>
       </c>
-      <c r="S245" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA245" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35129,22 +31479,12 @@
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR245" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS245" t="inlineStr"/>
       <c r="AT245" t="n">
         <v>0</v>
-      </c>
-      <c r="AU245" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
@@ -35253,11 +31593,6 @@
       <c r="R246" t="n">
         <v>0</v>
       </c>
-      <c r="S246" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA246" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35270,22 +31605,12 @@
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR246" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS246" t="inlineStr"/>
       <c r="AT246" t="n">
         <v>0</v>
-      </c>
-      <c r="AU246" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
@@ -35394,11 +31719,6 @@
       <c r="R247" t="n">
         <v>0</v>
       </c>
-      <c r="S247" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA247" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35411,22 +31731,12 @@
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR247" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS247" t="inlineStr"/>
       <c r="AT247" t="n">
         <v>0</v>
-      </c>
-      <c r="AU247" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
@@ -35535,11 +31845,6 @@
       <c r="R248" t="n">
         <v>0.0890209009502714</v>
       </c>
-      <c r="S248" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA248" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35552,22 +31857,12 @@
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR248" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS248" t="inlineStr"/>
       <c r="AT248" t="n">
         <v>0</v>
-      </c>
-      <c r="AU248" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
@@ -35676,11 +31971,6 @@
       <c r="R249" t="n">
         <v>0</v>
       </c>
-      <c r="S249" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA249" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35693,22 +31983,12 @@
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR249" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS249" t="inlineStr"/>
       <c r="AT249" t="n">
         <v>0</v>
-      </c>
-      <c r="AU249" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
@@ -35817,11 +32097,6 @@
       <c r="R250" t="n">
         <v>0</v>
       </c>
-      <c r="S250" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA250" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35834,22 +32109,12 @@
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR250" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS250" t="inlineStr"/>
       <c r="AT250" t="n">
         <v>0</v>
-      </c>
-      <c r="AU250" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
@@ -35958,11 +32223,6 @@
       <c r="R251" t="n">
         <v>0.4807379145086876</v>
       </c>
-      <c r="S251" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA251" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35975,22 +32235,12 @@
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR251" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS251" t="inlineStr"/>
       <c r="AT251" t="n">
         <v>0</v>
-      </c>
-      <c r="AU251" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
@@ -36099,11 +32349,6 @@
       <c r="R252" t="n">
         <v>0</v>
       </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA252" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36116,22 +32361,12 @@
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR252" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS252" t="inlineStr"/>
       <c r="AT252" t="n">
         <v>0</v>
-      </c>
-      <c r="AU252" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
